--- a/02_reports/node_b/NodeB_Candidates_ReviewQueue.xlsx
+++ b/02_reports/node_b/NodeB_Candidates_ReviewQueue.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -589,6 +589,118 @@
         </is>
       </c>
       <c r="L3" t="inlineStr">
+        <is>
+          <t>Ambiguous Node-B evidence (B3-only or weak match)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>High‐Gain Subnanowatt Power Consumption Hybrid Complementary Logic Inverter with WSe&lt;sub&gt;2&lt;/sub&gt; Nanosheet and ZnO Nanowire Transistors on Glass</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2014</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Seyed Hossein Hosseini Shokouh; Atiye Pezeshki; Syed Raza Ali Raza; Kwang H. Lee; Sung‐Wook Min; Pyo Jin Jeon; Jae Min Shin; Seongil Im</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>10.1002/adma.201403992</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1002/adma.201403992</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>B3_non_cmos_logic_context</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>OA_CITER</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>10.1021/nl302658y</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>2026-05-17T05:54:38.738824+00:00</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>A 1D–2D hybrid complementary logic inverter comprising of ZnO nanowire and WSe2 nanosheet field-effect transistors (FETs) is fabricated on glass, which shows excellent static and dynamic electrical performances with a voltage gain of ≈60, sub-nanowatt power consumption, and at least 1 kHz inverting speed. As a service to our authors and readers, this journal provides supporting information supplied by the authors. Such materials are peer reviewed and may be re-organized for online delivery, but are not copy-edited or typeset. Technical support issues arising from supporting information (other than missing files) should be addressed to the authors. Please note: The publisher is not responsible for the content or functionality of any supporting information supplied by the authors. Any queries (other than missing content) should be directed to the corresponding author for the article.</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Ambiguous Node-B evidence (B3-only or weak match)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>High‐Performance Hybrid Complementary Logic Inverter through Monolithic Integration of a MEMS Switch and an Oxide TFT</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2014</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Yong-Ha Song; Sang-Joon Ahn; Min-Wu Kim; J.S. Lee; Chi‐Sun Hwang; Jae‐Eun Pi; Seung‐Deok Ko; Kwang‐Wook Choi; Sang‐Hee Ko Park; Jun‐Bo Yoon</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>10.1002/smll.201402841</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1002/smll.201402841</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>B3_non_cmos_logic_context; mentions_p_channel; mentions_n_channel</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>OA_CITER</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10.1063/1.3483616</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>2026-05-17T05:56:21.930109+00:00</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>A hybrid complementary logic inverter consisting of a microelectromechanical system switch as a promising alternative for the p-type oxide thin film transistor (TFT) and an n-type oxide TFT is presented for ultralow power integrated circuits. These heterogeneous microdevices are monolithically integrated. The resulting logic device shows a distinctive voltage transfer characteristic curve, very low static leakage, zero-short circuit current, and exceedingly high voltage gain. As a service to our authors and readers, this journal provides supporting information supplied by the authors. Such materials are peer reviewed and may be re-organized for online delivery, but are not copy-edited or typeset. Technical support issues arising from supporting information (other than missing files) should be addressed to the authors. Please note: The publisher is not responsible for the content or functionality of any supporting information supplied by the authors. Any queries (other than missing content) should be directed to the corresponding author for the article.</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t>Ambiguous Node-B evidence (B3-only or weak match)</t>
         </is>
